--- a/unilabos/devices/workstation/bioyond_studio/bioyond_cell/20260323.xlsx
+++ b/unilabos/devices/workstation/bioyond_studio/bioyond_cell/20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UniLabdev\Uni-Lab-OS\unilabos\devices\workstation\bioyond_studio\bioyond_cell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEA7C67-8D86-47B4-9D4C-83B245D7B960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE48F75-1F17-45FD-8A0A-F327967E8632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>算法批次</t>
   </si>
@@ -123,6 +123,10 @@
   </si>
   <si>
     <t>TEST-6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>配液小瓶</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -133,7 +137,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0.000_);[Red]\(0.000\)"/>
-    <numFmt numFmtId="182" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -213,7 +217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,38 +237,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -605,96 +599,96 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="6">
         <v>46104</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4">
+        <v>80</v>
+      </c>
+      <c r="F2" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="K2" s="14">
+        <v>0.12</v>
+      </c>
+      <c r="L2" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="M2" s="14">
+        <v>2.65</v>
+      </c>
+      <c r="N2" s="14">
+        <v>1.25</v>
+      </c>
+      <c r="O2" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46104</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E3" s="4">
         <v>80</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F3" s="7">
         <v>2.5</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G3" s="4">
         <v>0</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="K2" s="18">
-        <v>0.12</v>
-      </c>
-      <c r="L2" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="M2" s="18">
-        <v>2.65</v>
-      </c>
-      <c r="N2" s="18">
-        <v>1.25</v>
-      </c>
-      <c r="O2" s="18">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.4">
-      <c r="A3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="15">
-        <v>46104</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="16">
-        <v>80</v>
-      </c>
-      <c r="F3" s="17">
-        <v>2.5</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="18">
+      <c r="J3" s="14">
         <v>0.19</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="14">
         <v>0.2</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="14">
         <v>0.15</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="14">
         <v>2.36</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="14">
         <v>1.5</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="14">
         <v>0.52</v>
       </c>
     </row>
